--- a/sheets/국악이꽃피는나무/검수/상주아리랑.xlsx
+++ b/sheets/국악이꽃피는나무/검수/상주아리랑.xlsx
@@ -3155,24 +3155,24 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="46.51" customHeight="true">
+    <row r="2" ht="48.19" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="69.11" customHeight="true">
+    <row r="3" ht="71.62" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="69.11" customHeight="true">
+    <row r="4" ht="71.62" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="69.11" customHeight="true">
+    <row r="5" ht="71.62" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" ht="69.11" customHeight="true">
+    <row r="6" ht="71.62" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="69.11" customHeight="true">
+    <row r="7" ht="71.62" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="69.11" customHeight="true">
+    <row r="8" ht="71.62" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" ht="69.11" customHeight="true">
+    <row r="9" ht="71.62" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="69.11" customHeight="true">
+    <row r="10" ht="71.62" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="69.11" customHeight="true">
+    <row r="11" ht="71.62" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="69.11" customHeight="true">
+    <row r="12" ht="71.62" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="69.11" customHeight="true">
+    <row r="13" ht="71.62" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="69.11" customHeight="true">
+    <row r="14" ht="71.62" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3857,6 +3857,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="86"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
 </worksheet>
 </file>